--- a/data/exp_raw/fe_analysis.xlsx
+++ b/data/exp_raw/fe_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vcantarella/Documents/FuhrbergerColumns/data/exp_raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/230e3d7962ef86ae/Kassel/prelim-lab-data/paul_lester/FuhrbergerColumns/data/exp_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C290CA-926E-E047-9F95-DA009F2A6262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{80C290CA-926E-E047-9F95-DA009F2A6262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F540A3-AFA5-45BF-8A68-4EC1B6160E41}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="880" windowWidth="27840" windowHeight="16180" xr2:uid="{C8071D3B-C586-244C-B46E-B25A50D33177}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8071D3B-C586-244C-B46E-B25A50D33177}"/>
   </bookViews>
   <sheets>
     <sheet name="fe_plate_1" sheetId="1" r:id="rId1"/>
@@ -92,12 +92,6 @@
     <t>C4 4-8</t>
   </si>
   <si>
-    <t>T0 - 1</t>
-  </si>
-  <si>
-    <t>T0 - 2</t>
-  </si>
-  <si>
     <t>val1 fe2+</t>
   </si>
   <si>
@@ -144,6 +138,12 @@
   </si>
   <si>
     <t>weight_error</t>
+  </si>
+  <si>
+    <t>Br 17-18_2</t>
+  </si>
+  <si>
+    <t>Br 17-18_1</t>
   </si>
 </sst>
 </file>
@@ -1607,38 +1607,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E2489AC-82C2-7345-9BAC-7A6CD6AD2B1F}">
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>24</v>
-      </c>
-      <c r="G1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" t="s">
-        <v>26</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
@@ -1647,22 +1647,22 @@
         <v>2</v>
       </c>
       <c r="K1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>28</v>
       </c>
-      <c r="M1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" t="s">
-        <v>30</v>
-      </c>
       <c r="O1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R1" t="s">
         <v>3</v>
@@ -1680,13 +1680,13 @@
         <v>7</v>
       </c>
       <c r="X1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Y1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1712,11 +1712,11 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <f>(AVERAGE(B2:D2)*$T$11 + $T$12)*H2</f>
+        <f t="shared" ref="J2:J11" si="0">(AVERAGE(B2:D2)*$T$11 + $T$12)*H2</f>
         <v>6387.7624337900124</v>
       </c>
       <c r="K2">
-        <f>(AVERAGE(E2:G2)*$T$21 + $T$22)*H2</f>
+        <f t="shared" ref="K2:K11" si="1">(AVERAGE(E2:G2)*$T$21 + $T$22)*H2</f>
         <v>10502.098390578023</v>
       </c>
       <c r="L2">
@@ -1727,11 +1727,11 @@
         <v>18.094000000000001</v>
       </c>
       <c r="N2">
-        <f>M2-$X$2</f>
+        <f t="shared" ref="N2:N11" si="2">M2-$X$2</f>
         <v>5.1740000000000013</v>
       </c>
       <c r="O2">
-        <f>J2*$X$4/1000/(N2/1000)*0.000001</f>
+        <f t="shared" ref="O2:O11" si="3">J2*$X$4/1000/(N2/1000)*0.000001</f>
         <v>1.2345887966351004E-2</v>
       </c>
       <c r="P2">
@@ -1761,7 +1761,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1787,30 +1787,30 @@
         <v>20</v>
       </c>
       <c r="J3">
-        <f>(AVERAGE(B3:D3)*$T$11 + $T$12)*H3</f>
+        <f t="shared" si="0"/>
         <v>9913.127466631453</v>
       </c>
       <c r="K3">
-        <f>(AVERAGE(E3:G3)*$T$21 + $T$22)*H3</f>
+        <f t="shared" si="1"/>
         <v>15747.175530518378</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L11" si="0">K3-J3</f>
+        <f t="shared" ref="L3:L11" si="4">K3-J3</f>
         <v>5834.0480638869249</v>
       </c>
       <c r="M3">
         <v>19.338999999999999</v>
       </c>
       <c r="N3">
-        <f>M3-$X$2</f>
+        <f t="shared" si="2"/>
         <v>6.4189999999999987</v>
       </c>
       <c r="O3">
-        <f>J3*$X$4/1000/(N3/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.5443414031206505E-2</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="1">L3*$X$4/1000/(M3/1000)*0.000001</f>
+        <f t="shared" ref="P3:P11" si="5">L3*$X$4/1000/(M3/1000)*0.000001</f>
         <v>3.0167268544841644E-3</v>
       </c>
       <c r="R3">
@@ -1826,14 +1826,14 @@
         <v>0.70599999999999996</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:V5" si="2">AVERAGE(S3:U3)</f>
+        <f t="shared" ref="V3:V5" si="6">AVERAGE(S3:U3)</f>
         <v>0.70866666666666667</v>
       </c>
       <c r="X3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1859,30 +1859,30 @@
         <v>20</v>
       </c>
       <c r="J4">
-        <f>(AVERAGE(B4:D4)*$T$11 + $T$12)*H4</f>
+        <f t="shared" si="0"/>
         <v>6038.6203672637648</v>
       </c>
       <c r="K4">
-        <f>(AVERAGE(E4:G4)*$T$21 + $T$22)*H4</f>
+        <f t="shared" si="1"/>
         <v>11901.067394059297</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5862.4470267955321</v>
       </c>
       <c r="M4">
         <v>18.739999999999998</v>
       </c>
       <c r="N4">
-        <f>M4-$X$2</f>
+        <f t="shared" si="2"/>
         <v>5.8199999999999985</v>
       </c>
       <c r="O4">
-        <f>J4*$X$4/1000/(N4/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.0375636369869014E-2</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.1283068446080749E-3</v>
       </c>
       <c r="R4">
@@ -1898,14 +1898,14 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="V4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.34533333333333333</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1931,30 +1931,30 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <f>(AVERAGE(B5:D5)*$T$11 + $T$12)*H5</f>
+        <f t="shared" si="0"/>
         <v>8240.1550645265052</v>
       </c>
       <c r="K5">
-        <f>(AVERAGE(E5:G5)*$T$21 + $T$22)*H5</f>
+        <f t="shared" si="1"/>
         <v>16554.43558992902</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8314.2805254025152</v>
       </c>
       <c r="M5">
         <v>17.84</v>
       </c>
       <c r="N5">
-        <f>M5-$X$2</f>
+        <f t="shared" si="2"/>
         <v>4.92</v>
       </c>
       <c r="O5">
-        <f>J5*$X$4/1000/(N5/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.6748282651476636E-2</v>
       </c>
       <c r="P5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4.6604711465260736E-3</v>
       </c>
       <c r="R5">
@@ -1970,11 +1970,11 @@
         <v>0.18</v>
       </c>
       <c r="V5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.19133333333333336</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1994,34 +1994,34 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <f>(AVERAGE(B6:D6)*$T$11 + $T$12)*H6</f>
+        <f t="shared" si="0"/>
         <v>8203.7860992633541</v>
       </c>
       <c r="K6">
-        <f>(AVERAGE(E6:G6)*$T$21 + $T$22)*H6</f>
+        <f t="shared" si="1"/>
         <v>13378.226508007039</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5174.4404087436851</v>
       </c>
       <c r="M6">
         <v>17.571999999999999</v>
       </c>
       <c r="N6">
-        <f>M6-$X$2</f>
+        <f t="shared" si="2"/>
         <v>4.6519999999999992</v>
       </c>
       <c r="O6">
-        <f>J6*$X$4/1000/(N6/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.7634965819568693E-2</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.944707721798136E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2047,34 +2047,34 @@
         <v>20</v>
       </c>
       <c r="J7">
-        <f>(AVERAGE(B7:D7)*$T$11 + $T$12)*H7</f>
+        <f t="shared" si="0"/>
         <v>6693.2617420004826</v>
       </c>
       <c r="K7">
-        <f>(AVERAGE(E7:G7)*$T$21 + $T$22)*H7</f>
+        <f t="shared" si="1"/>
         <v>15032.898305175975</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8339.6365631754925</v>
       </c>
       <c r="M7">
         <v>18.286999999999999</v>
       </c>
       <c r="N7">
-        <f>M7-$X$2</f>
+        <f t="shared" si="2"/>
         <v>5.3669999999999991</v>
       </c>
       <c r="O7">
-        <f>J7*$X$4/1000/(N7/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.2471141684368333E-2</v>
       </c>
       <c r="P7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4.5604180910895674E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2100,34 +2100,34 @@
         <v>20</v>
       </c>
       <c r="J8">
-        <f>(AVERAGE(B8:D8)*$T$11 + $T$12)*H8</f>
+        <f t="shared" si="0"/>
         <v>6814.4916262109846</v>
       </c>
       <c r="K8">
-        <f>(AVERAGE(E8:G8)*$T$21 + $T$22)*H8</f>
+        <f t="shared" si="1"/>
         <v>11021.956962868646</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4207.4653366576613</v>
       </c>
       <c r="M8">
         <v>18.170000000000002</v>
       </c>
       <c r="N8">
-        <f>M8-$X$2</f>
+        <f t="shared" si="2"/>
         <v>5.2500000000000018</v>
       </c>
       <c r="O8">
-        <f>J8*$X$4/1000/(N8/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.2979984049925678E-2</v>
       </c>
       <c r="P8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>2.3156110823652504E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2153,36 +2153,36 @@
         <v>40</v>
       </c>
       <c r="J9">
-        <f>(AVERAGE(B9:D9)*$T$11 + $T$12)*H9</f>
+        <f t="shared" si="0"/>
         <v>17595.625063789641</v>
       </c>
       <c r="K9">
-        <f>(AVERAGE(E9:G9)*$T$21 + $T$22)*H9</f>
+        <f t="shared" si="1"/>
         <v>23658.43404455858</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6062.8089807689394</v>
       </c>
       <c r="M9">
         <v>17.77</v>
       </c>
       <c r="N9">
-        <f>M9-$X$2</f>
+        <f t="shared" si="2"/>
         <v>4.8499999999999996</v>
       </c>
       <c r="O9">
-        <f>J9*$X$4/1000/(N9/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>3.6279639306782768E-2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.4118227241243322E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>0.39</v>
@@ -2206,36 +2206,36 @@
         <v>20</v>
       </c>
       <c r="J10">
-        <f>(AVERAGE(B10:D10)*$T$11 + $T$12)*H10</f>
+        <f t="shared" si="0"/>
         <v>5354.8838203165251</v>
       </c>
       <c r="K10">
-        <f>(AVERAGE(E10:G10)*$T$21 + $T$22)*H10</f>
+        <f t="shared" si="1"/>
         <v>11114.939796936889</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5760.0559766203642</v>
       </c>
       <c r="M10">
         <v>17.553999999999998</v>
       </c>
       <c r="N10">
-        <f>M10-$X$2</f>
+        <f t="shared" si="2"/>
         <v>4.6339999999999986</v>
       </c>
       <c r="O10">
-        <f>J10*$X$4/1000/(N10/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.1555640527225998E-2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.2813352948731708E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>0.628</v>
@@ -2259,30 +2259,30 @@
         <v>20</v>
       </c>
       <c r="J11">
-        <f>(AVERAGE(B11:D11)*$T$11 + $T$12)*H11</f>
+        <f t="shared" si="0"/>
         <v>8788.1141411579811</v>
       </c>
       <c r="K11">
-        <f>(AVERAGE(E11:G11)*$T$21 + $T$22)*H11</f>
+        <f t="shared" si="1"/>
         <v>15041.35129009127</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6253.2371489332891</v>
       </c>
       <c r="M11">
         <v>18.9938</v>
       </c>
       <c r="N11">
-        <f>M11-$X$2</f>
+        <f t="shared" si="2"/>
         <v>6.0738000000000003</v>
       </c>
       <c r="O11">
-        <f>J11*$X$4/1000/(N11/1000)*0.000001</f>
+        <f t="shared" si="3"/>
         <v>1.4468889560337811E-2</v>
       </c>
       <c r="P11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3.2922517605393805E-3</v>
       </c>
       <c r="S11" t="s">
@@ -2293,18 +2293,18 @@
         <v>727.37930526302046</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="T12">
         <f>INTERCEPT(R2:R5,V2:V5)</f>
         <v>-20.055554099908875</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R15" t="s">
         <v>3</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="R16">
         <v>1000</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>1.7249999999999999</v>
       </c>
     </row>
-    <row r="17" spans="18:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="18:22" x14ac:dyDescent="0.25">
       <c r="R17">
         <v>500</v>
       </c>
@@ -2353,11 +2353,11 @@
         <v>0.94299999999999995</v>
       </c>
       <c r="V17">
-        <f t="shared" ref="V17:V19" si="3">AVERAGE(S17:U17)</f>
+        <f t="shared" ref="V17:V19" si="7">AVERAGE(S17:U17)</f>
         <v>0.91233333333333333</v>
       </c>
     </row>
-    <row r="18" spans="18:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="18:22" x14ac:dyDescent="0.25">
       <c r="R18">
         <v>250</v>
       </c>
@@ -2371,11 +2371,11 @@
         <v>0.53500000000000003</v>
       </c>
       <c r="V18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.54366666666666674</v>
       </c>
     </row>
-    <row r="19" spans="18:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="18:22" x14ac:dyDescent="0.25">
       <c r="R19">
         <v>100</v>
       </c>
@@ -2389,11 +2389,11 @@
         <v>0.32</v>
       </c>
       <c r="V19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.30266666666666664</v>
       </c>
     </row>
-    <row r="21" spans="18:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="18:22" x14ac:dyDescent="0.25">
       <c r="S21" t="s">
         <v>8</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>633.9738686471012</v>
       </c>
     </row>
-    <row r="22" spans="18:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="18:22" x14ac:dyDescent="0.25">
       <c r="T22">
         <f>INTERCEPT(R16:R19,V16:V19)</f>
         <v>-89.63840843590458</v>
